--- a/Result/profitability/2382.xlsx
+++ b/Result/profitability/2382.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.16</v>
       </c>
       <c r="M2" t="n">
-        <v>4.31875</v>
+        <v>4.7075</v>
       </c>
       <c r="N2" t="n">
-        <v>6.60875</v>
+        <v>6.32</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.38</v>
       </c>
       <c r="M3" t="n">
-        <v>3.95125</v>
+        <v>4.364999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>6.26625</v>
+        <v>5.962499999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.98</v>
       </c>
       <c r="M4" t="n">
-        <v>3.68375</v>
+        <v>3.98</v>
       </c>
       <c r="N4" t="n">
-        <v>6.065</v>
+        <v>5.7025</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>1.1</v>
       </c>
       <c r="M5" t="n">
-        <v>3.18875</v>
+        <v>3.57125</v>
       </c>
       <c r="N5" t="n">
-        <v>5.69375</v>
+        <v>5.44</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.22</v>
       </c>
       <c r="M6" t="n">
-        <v>2.795</v>
+        <v>3.19125</v>
       </c>
       <c r="N6" t="n">
-        <v>5.53875</v>
+        <v>5.31</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.34</v>
       </c>
       <c r="M7" t="n">
-        <v>2.43</v>
+        <v>2.63875</v>
       </c>
       <c r="N7" t="n">
-        <v>5.453749999999999</v>
+        <v>5.29</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.68</v>
       </c>
       <c r="M8" t="n">
-        <v>1.92</v>
+        <v>2.16125</v>
       </c>
       <c r="N8" t="n">
-        <v>5.40375</v>
+        <v>5.43375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>1.49625</v>
       </c>
       <c r="N11" t="n">
-        <v>5.074999999999999</v>
+        <v>5.075</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1036593</v>
+      </c>
+      <c r="D75" t="n">
+        <v>984514</v>
+      </c>
+      <c r="E75" t="n">
+        <v>52079</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="G75" t="n">
+        <v>34244</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.30%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2317</v>
+      </c>
+      <c r="J75" t="n">
+        <v>36561</v>
+      </c>
+      <c r="K75" t="n">
+        <v>28651</v>
+      </c>
+      <c r="L75" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="M75" t="n">
+        <v>5.102499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6.59125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3509090909090908</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.2399999999999993</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05020920502092041</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.700228832951945</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2879432624113476</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
